--- a/data/5.Psicologos/leads_psicologo_completo.xlsx
+++ b/data/5.Psicologos/leads_psicologo_completo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06ae8d044cc0a8d9/Documentos/GitHub/Leads_sheacher/data/5.Psicologos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejgar\OneDrive\Documentos\GitHub\Leads_sheacher\data\5.Psicologos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_3DD5D1B5D3F05A5F53BB2D11595ED87656CD5C7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCE5AE4B-57BB-4CF2-BB45-8172F45BA23E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA259276-DC9E-4E95-B4FE-C4016D2B112E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="864" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="357">
   <si>
     <t>Nombre</t>
   </si>
@@ -1104,6 +1104,9 @@
   </si>
   <si>
     <t>info@ammapsicologia.es;hola@hablapsicologia.com;info@psicoform360.es;info@ponspsicologia.com;info@tupsicoterapiamadrid.com;contacto@psicotep.com;mmoragon@cop.es;I_estaun@imagen10.com;info@mensalud.com;info@elvisopsicologos.com;equipoactua@gmail.com;info@aitta.es;nuestropsicologo.citas@gmail.com;info@silviasanzpsicologa.com;info@rospsicologia.com;administrador@centropsintegra.com;info@symbolpsicologia.com;user@domain.com;consulta@psicologiabayli.com;soporte@doctoralia.com;contacto@enequilibriomental.net;clinica@institutopsicode.com;centropsicologicosmc@gmail.com;info@supiha.com;nuestropsicologo.citas@gmail.com;anarodrigo.psicologa@gmail.com;consulta@cgpsicologia.com;info@tuyopsicologos.com;manuel@psicologiamadrid.net;%20contacto@arbolato.com;center@centerpsicologia.com;edulaz@cop.es;psikids-pozuelo@psikids.es;info@psicologiamadrid.es;contacto@antestupsicologia.com;605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com;info@alceapsicologia.com;info@sandrahernandezpsicologa.com;carolina.alvarez@psicoanalitica.com;info@psicolaume.com</t>
+  </si>
+  <si>
+    <t>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com;info@avancepsicologos.com;info@implicapsicologia.com;605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
   </si>
 </sst>
 </file>
@@ -3147,7 +3150,7 @@
       <c r="G62" t="s">
         <v>13</v>
       </c>
-      <c r="H62" t="str">
+      <c r="H62" s="3" t="str">
         <f>E62</f>
         <v>info@somospsicologos.es</v>
       </c>
@@ -3174,7 +3177,7 @@
       <c r="G63" t="s">
         <v>13</v>
       </c>
-      <c r="H63" t="str">
+      <c r="H63" s="3" t="str">
         <f t="shared" si="0"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es</v>
       </c>
@@ -3201,7 +3204,7 @@
       <c r="G64" t="s">
         <v>13</v>
       </c>
-      <c r="H64" t="str">
+      <c r="H64" s="3" t="str">
         <f t="shared" si="0"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es</v>
       </c>
@@ -3228,7 +3231,7 @@
       <c r="G65" t="s">
         <v>13</v>
       </c>
-      <c r="H65" t="str">
+      <c r="H65" s="3" t="str">
         <f t="shared" si="0"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com</v>
       </c>
@@ -3255,7 +3258,7 @@
       <c r="G66" t="s">
         <v>13</v>
       </c>
-      <c r="H66" t="str">
+      <c r="H66" s="3" t="str">
         <f t="shared" si="0"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es</v>
       </c>
@@ -3282,7 +3285,7 @@
       <c r="G67" t="s">
         <v>13</v>
       </c>
-      <c r="H67" t="str">
+      <c r="H67" s="3" t="str">
         <f t="shared" si="0"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com</v>
       </c>
@@ -3309,7 +3312,7 @@
       <c r="G68" t="s">
         <v>13</v>
       </c>
-      <c r="H68" t="str">
+      <c r="H68" s="3" t="str">
         <f t="shared" ref="H68:H72" si="1">H67&amp;";"&amp;E68</f>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com</v>
       </c>
@@ -3336,7 +3339,7 @@
       <c r="G69" t="s">
         <v>13</v>
       </c>
-      <c r="H69" t="str">
+      <c r="H69" s="3" t="str">
         <f t="shared" si="1"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com</v>
       </c>
@@ -3363,7 +3366,7 @@
       <c r="G70" t="s">
         <v>13</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H70" s="3" t="str">
         <f t="shared" si="1"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com;info@avancepsicologos.com</v>
       </c>
@@ -3390,7 +3393,7 @@
       <c r="G71" t="s">
         <v>13</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H71" s="3" t="str">
         <f t="shared" si="1"/>
         <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com;info@avancepsicologos.com;info@implicapsicologia.com</v>
       </c>
@@ -3417,9 +3420,8 @@
       <c r="G72" t="s">
         <v>13</v>
       </c>
-      <c r="H72" t="str">
-        <f t="shared" si="1"/>
-        <v>info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com;info@avancepsicologos.com;info@implicapsicologia.com;605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</v>
+      <c r="H72" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
@@ -3431,8 +3433,9 @@
     <hyperlink ref="E24" r:id="rId1" display="mailto:info@psicoform360.es" xr:uid="{11337DE9-135C-4A99-925D-A2C4DBEB819A}"/>
     <hyperlink ref="E9" r:id="rId2" display="mailto:laurarabascog@gmail.com" xr:uid="{E6C8984F-1C59-4932-BCB3-302CA7D09AAB}"/>
     <hyperlink ref="H41" r:id="rId3" display="info@ammapsicologia.es;hola@hablapsicologia.com;info@psicoform360.es;info@ponspsicologia.com;info@tupsicoterapiamadrid.com;contacto@psicotep.com;mmoragon@cop.es;I_estaun@imagen10.com;info@mensalud.com;info@elvisopsicologos.com;equipoactua@gmail.com;info@aitta.es;nuestropsicologo.citas@gmail.com;info@silviasanzpsicologa.com;info@rospsicologia.com;administrador@centropsintegra.com;info@symbolpsicologia.com;user@domain.com;consulta@psicologiabayli.com;soporte@doctoralia.com" xr:uid="{D0E9B5F8-550B-4719-8971-2C82A6780622}"/>
+    <hyperlink ref="H72" r:id="rId4" display="info@somospsicologos.es;info@calmaperinatal.es;info@elpradopsicologos.es;mariamontespsicoterapia@gmail.com;info@basepsicologia.es;contacto@afpsicologia.com;nombre@email.com;%20contacto@institutoclaritas.com;info@avancepsicologos.com;info@implicapsicologia.com;605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com" xr:uid="{FCA4E7CD-1303-4BA3-901D-164D55835872}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId5"/>
 </worksheet>
 </file>